--- a/Data/ID_Generators/SPAIN_IDGenerator.xlsx
+++ b/Data/ID_Generators/SPAIN_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0490EBAE-33F3-490C-9E56-CFC1FBD320CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D252D2C9-F0BD-4546-8C9F-7A36297F0195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="69">
   <si>
     <t>AddEditID1</t>
   </si>
@@ -231,6 +231,18 @@
   </si>
   <si>
     <t>10006462A</t>
+  </si>
+  <si>
+    <t>10006463A</t>
+  </si>
+  <si>
+    <t>10006464A</t>
+  </si>
+  <si>
+    <t>10006465A</t>
+  </si>
+  <si>
+    <t>10006466A</t>
   </si>
 </sst>
 </file>
@@ -611,7 +623,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F63" si="0">D3&amp;E3</f>
+        <f t="shared" ref="F3:F66" si="0">D3&amp;E3</f>
         <v>10006402A</v>
       </c>
     </row>
@@ -1696,66 +1708,118 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="2"/>
-      <c r="D64" s="2"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-      <c r="D65" s="2"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="2"/>
-      <c r="D66" s="2"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="2"/>
-      <c r="D67" s="2"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>281000757178</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="2">
+        <v>10006463</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="0"/>
+        <v>10006463A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>281000757279</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D65" s="2">
+        <v>10006464</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="0"/>
+        <v>10006464A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>281000757380</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D66" s="2">
+        <v>10006465</v>
+      </c>
+      <c r="E66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="0"/>
+        <v>10006465A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>281000757481</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" s="2">
+        <v>10006466</v>
+      </c>
+      <c r="E67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" ref="F67" si="1">D67&amp;E67</f>
+        <v>10006466A</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="D76" s="2"/>
